--- a/topic01-introduction/calendar-fp-26.xlsx
+++ b/topic01-introduction/calendar-fp-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maireadmeagher/Documents/GitRepos/fun-prog-26/topic01-introduction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A008AC92-2491-D445-8AD6-4CE0B4C54A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDBB5FE-1A73-C84C-864D-D75C61948553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="2700" windowWidth="27040" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1180" windowWidth="27040" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calendar-1" sheetId="2" r:id="rId1"/>
@@ -1723,9 +1723,7 @@
       <c r="C6" s="11"/>
       <c r="D6" s="36"/>
       <c r="E6" s="11"/>
-      <c r="F6" s="32" t="s">
-        <v>6</v>
-      </c>
+      <c r="F6" s="28"/>
     </row>
     <row r="7" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="13"/>
@@ -1735,7 +1733,9 @@
       <c r="C7" s="11"/>
       <c r="D7" s="36"/>
       <c r="E7" s="12"/>
-      <c r="F7" s="28"/>
+      <c r="F7" s="32" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="14"/>
